--- a/output/pdf_financials_xlsx/BR.xlsx
+++ b/output/pdf_financials_xlsx/BR.xlsx
@@ -5292,7 +5292,7 @@
         <v>0.892</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1.255</v>
+        <v>2.51</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>1.255</v>

--- a/output/pdf_financials_xlsx/BR.xlsx
+++ b/output/pdf_financials_xlsx/BR.xlsx
@@ -2182,49 +2182,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.281</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.317</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>-0.354</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>-1.902</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.612</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.039</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="35">
@@ -2286,49 +2286,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.281</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.317</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>-0.354</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>-1.902</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.612</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.039</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="37">
@@ -2910,49 +2910,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.033</v>
+        <v>0.305</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.872</v>
+        <v>0.217</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.645</v>
+        <v>0.364</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.071</v>
+        <v>0.754</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.113</v>
+        <v>1.573</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.095</v>
+        <v>0.555</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.436</v>
+        <v>2.229</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.537</v>
+        <v>0.369</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.39</v>
+        <v>2.744</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.463</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.606</v>
+        <v>0.994</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.758</v>
+        <v>1.719</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.812</v>
+        <v>1.44</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.061</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="49">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -30187,7 +30187,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E254" s="5" t="n">

--- a/output/pdf_financials_xlsx/BR.xlsx
+++ b/output/pdf_financials_xlsx/BR.xlsx
@@ -579,10 +579,8 @@
       <c r="J4" s="3" t="n">
         <v>48.748</v>
       </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="3" t="n">
+        <v>46.573</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>45.982</v>
@@ -633,10 +631,8 @@
       <c r="J5" s="3" t="n">
         <v>27.936</v>
       </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>31.16</v>
@@ -687,10 +683,8 @@
       <c r="J6" s="3" t="n">
         <v>20.812</v>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="3" t="n">
+        <v>46.573</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>14.822</v>
@@ -741,10 +735,8 @@
       <c r="J7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0</v>
@@ -795,10 +787,8 @@
       <c r="J8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -849,10 +839,8 @@
       <c r="J9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0</v>
@@ -903,10 +891,8 @@
       <c r="J10" s="3" t="n">
         <v>19.881</v>
       </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>16.833</v>
@@ -957,10 +943,8 @@
       <c r="J11" s="3" t="n">
         <v>0.931</v>
       </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K11" s="3" t="n">
+        <v>46.573</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-2.011</v>
@@ -1011,10 +995,8 @@
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1065,10 +1047,8 @@
       <c r="J13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>-0</v>
@@ -1119,10 +1099,8 @@
       <c r="J14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>0</v>
@@ -1173,10 +1151,8 @@
       <c r="J15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>0</v>
@@ -1281,10 +1257,8 @@
       <c r="J17" s="3" t="n">
         <v>-0.262</v>
       </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>0.819</v>
@@ -1553,10 +1527,8 @@
       <c r="J21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -1607,10 +1579,8 @@
       <c r="J22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>0</v>
@@ -1931,10 +1901,8 @@
       <c r="J28" s="3" t="n">
         <v>0.524</v>
       </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0.664</v>
@@ -2497,46 +2465,46 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.392</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.279</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.287</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="41">
@@ -2549,46 +2517,46 @@
         <v>3.617</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2.788</v>
+        <v>3.017</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2.358</v>
+        <v>2.497</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.353</v>
+        <v>1.589</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.221</v>
+        <v>2.467</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2.221</v>
+        <v>2.409</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.294</v>
+        <v>1.472</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.164</v>
+        <v>3.556</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3.384</v>
+        <v>3.663</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>2.167</v>
+        <v>2.499</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>2.549</v>
+        <v>2.836</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>2.933</v>
+        <v>3.385</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>2.804</v>
+        <v>3.01</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.779</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="42">
@@ -2913,46 +2881,46 @@
         <v>0.305</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.364</v>
+        <v>0.225</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.754</v>
+        <v>0.518</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.573</v>
+        <v>1.327</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.555</v>
+        <v>0.367</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.229</v>
+        <v>2.051</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.369</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.744</v>
+        <v>2.465</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.463</v>
+        <v>0.131</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.994</v>
+        <v>0.707</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.719</v>
+        <v>1.267</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.44</v>
+        <v>1.234</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.524</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="49">
@@ -3805,19 +3773,19 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>1.187</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>4.611</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>6.341</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>4.146</v>
       </c>
       <c r="P64" s="3" t="n">
         <v>0</v>
@@ -4013,7 +3981,7 @@
         <v>4.682</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>1.187</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>5.753</v>
@@ -7631,7 +7599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S573"/>
+  <dimension ref="A1:S578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34715,7 +34683,11 @@
           <t>Deferred income tax (recovery) 8</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -40210,7 +40182,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E365" s="5" t="n">
         <v>-0.658</v>
       </c>
@@ -44711,7 +44687,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -47941,7 +47921,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -53073,14 +53057,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
+      <c r="B510" t="inlineStr"/>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Net revenue 4 $</t>
+          <t>Net revenue $ 42,653 $</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -53118,19 +53098,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K510" s="5" t="n">
-        <v>43.126</v>
-      </c>
-      <c r="L510" s="5" t="n">
-        <v>46.573</v>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M510" s="5" t="n">
         <v>48.748</v>
       </c>
-      <c r="N510" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N510" s="5" t="n">
+        <v>46.573</v>
       </c>
       <c r="O510" t="inlineStr">
         <is>
@@ -53164,21 +53146,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
+      <c r="B511" t="inlineStr"/>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Cost of sales 5</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>EBITDA(2) (1,062)</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -53209,19 +53183,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K511" s="5" t="n">
-        <v>24.477</v>
-      </c>
-      <c r="L511" s="5" t="n">
-        <v>27.676</v>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M511" s="5" t="n">
-        <v>27.936</v>
-      </c>
-      <c r="N511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.15</v>
+      </c>
+      <c r="N511" s="5" t="n">
+        <v>1.907</v>
       </c>
       <c r="O511" t="inlineStr">
         <is>
@@ -53255,21 +53231,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B512" t="inlineStr"/>
       <c r="C512" t="inlineStr">
         <is>
-          <t>General and administrative 7</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Operating profit (loss) (5,100)</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -53300,19 +53268,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K512" s="5" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="L512" s="5" t="n">
-        <v>5.174</v>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M512" s="5" t="n">
-        <v>5.795</v>
-      </c>
-      <c r="N512" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.931</v>
+      </c>
+      <c r="N512" s="5" t="n">
+        <v>-1.037</v>
       </c>
       <c r="O512" t="inlineStr">
         <is>
@@ -53346,52 +53316,58 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B513" t="inlineStr"/>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E513" s="5" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="F513" s="5" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="G513" s="5" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="H513" s="5" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="I513" s="5" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="J513" s="5" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="K513" s="5" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="L513" s="5" t="n">
-        <v>0.47</v>
+          <t>Net income (loss) (2,922)</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M513" s="5" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="N513" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.36</v>
+      </c>
+      <c r="N513" s="5" t="n">
+        <v>-1.02</v>
       </c>
       <c r="O513" t="inlineStr">
         <is>
@@ -53425,21 +53401,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B514" t="inlineStr"/>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Operating income (loss)</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Per share – basic and diluted $ (0.42) $</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>
@@ -53475,16 +53443,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L514" s="5" t="n">
-        <v>-1.037</v>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M514" s="5" t="n">
-        <v>0.931</v>
-      </c>
-      <c r="N514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-08</v>
+      </c>
+      <c r="N514" s="5" t="n">
+        <v>-1.5e-07</v>
       </c>
       <c r="O514" t="inlineStr">
         <is>
@@ -53520,15 +53488,19 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Finance expenses 8</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr"/>
+          <t>Net revenue 4 $</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -53554,17 +53526,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J515" s="5" t="n">
-        <v>0.18</v>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K515" s="5" t="n">
-        <v>0.349</v>
+        <v>43.126</v>
       </c>
       <c r="L515" s="5" t="n">
-        <v>0.333</v>
+        <v>46.573</v>
       </c>
       <c r="M515" s="5" t="n">
-        <v>0.327</v>
+        <v>48.748</v>
       </c>
       <c r="N515" t="inlineStr">
         <is>
@@ -53605,15 +53579,19 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr"/>
+          <t>Cost of sales 5</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>-</t>
@@ -53644,16 +53622,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K516" s="5" t="n">
+        <v>24.477</v>
       </c>
       <c r="L516" s="5" t="n">
-        <v>0.002</v>
+        <v>27.676</v>
       </c>
       <c r="M516" s="5" t="n">
-        <v>0.018</v>
+        <v>27.936</v>
       </c>
       <c r="N516" t="inlineStr">
         <is>
@@ -53699,19 +53675,23 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
+          <t>General and administrative 7</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E517" s="5" t="n">
-        <v>-8.856</v>
-      </c>
-      <c r="F517" s="5" t="n">
-        <v>3.49</v>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
@@ -53723,22 +53703,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I517" s="5" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="J517" s="5" t="n">
-        <v>-0.951</v>
-      </c>
-      <c r="K517" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K517" s="5" t="n">
+        <v>5.72</v>
       </c>
       <c r="L517" s="5" t="n">
-        <v>-1.368</v>
+        <v>5.174</v>
       </c>
       <c r="M517" s="5" t="n">
-        <v>0.622</v>
+        <v>5.795</v>
       </c>
       <c r="N517" t="inlineStr">
         <is>
@@ -53779,51 +53761,45 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)                              9</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr"/>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E518" s="5" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="F518" s="5" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="G518" s="5" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="H518" s="5" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="I518" s="5" t="n">
+        <v>0.286</v>
       </c>
       <c r="J518" s="5" t="n">
-        <v>0.275</v>
+        <v>0.376</v>
       </c>
       <c r="K518" s="5" t="n">
-        <v>-0.272</v>
+        <v>0.548</v>
       </c>
       <c r="L518" s="5" t="n">
-        <v>-0.175</v>
+        <v>0.47</v>
       </c>
       <c r="M518" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.524</v>
       </c>
       <c r="N518" t="inlineStr">
         <is>
@@ -53864,15 +53840,19 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)                              9</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr"/>
+          <t>Operating income (loss)</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -53898,17 +53878,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J519" s="5" t="n">
-        <v>-0.151</v>
-      </c>
-      <c r="K519" s="5" t="n">
-        <v>0.233</v>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L519" s="5" t="n">
-        <v>-0.173</v>
+        <v>-1.037</v>
       </c>
       <c r="M519" s="5" t="n">
-        <v>0.333</v>
+        <v>0.931</v>
       </c>
       <c r="N519" t="inlineStr">
         <is>
@@ -53949,12 +53933,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)                              9</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)                              9 total</t>
+          <t>Finance expenses 8</t>
         </is>
       </c>
       <c r="D520" t="inlineStr"/>
@@ -53984,16 +53968,16 @@
         </is>
       </c>
       <c r="J520" s="5" t="n">
-        <v>0.124</v>
+        <v>0.18</v>
       </c>
       <c r="K520" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.349</v>
       </c>
       <c r="L520" s="5" t="n">
-        <v>-0.348</v>
+        <v>0.333</v>
       </c>
       <c r="M520" s="5" t="n">
-        <v>0.262</v>
+        <v>0.327</v>
       </c>
       <c r="N520" t="inlineStr">
         <is>
@@ -54034,19 +54018,15 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)                              9</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) $</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -54083,10 +54063,10 @@
         </is>
       </c>
       <c r="L521" s="5" t="n">
-        <v>-1.02</v>
+        <v>0.002</v>
       </c>
       <c r="M521" s="5" t="n">
-        <v>0.36</v>
+        <v>0.018</v>
       </c>
       <c r="N521" t="inlineStr">
         <is>
@@ -54127,28 +54107,24 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Per share amounts</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Basic and diluted 10 $</t>
+          <t>Income (loss) before income taxes</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E522" s="5" t="n">
+        <v>-8.856</v>
+      </c>
+      <c r="F522" s="5" t="n">
+        <v>3.49</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
@@ -54160,15 +54136,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I522" s="5" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="J522" s="5" t="n">
+        <v>-0.951</v>
       </c>
       <c r="K522" t="inlineStr">
         <is>
@@ -54176,10 +54148,10 @@
         </is>
       </c>
       <c r="L522" s="5" t="n">
-        <v>-1.5e-07</v>
+        <v>-1.368</v>
       </c>
       <c r="M522" s="5" t="n">
-        <v>5e-08</v>
+        <v>0.622</v>
       </c>
       <c r="N522" t="inlineStr">
         <is>
@@ -54220,12 +54192,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Finance expenses include the following</t>
+          <t>Income tax expense (recovery)                              9</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Interest on Operating Facility $</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D523" t="inlineStr"/>
@@ -54254,21 +54226,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J523" s="5" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K523" s="5" t="n">
+        <v>-0.272</v>
       </c>
       <c r="L523" s="5" t="n">
-        <v>0.055</v>
+        <v>-0.175</v>
       </c>
       <c r="M523" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="N523" t="inlineStr">
         <is>
@@ -54309,12 +54277,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Finance expenses include the following</t>
+          <t>Income tax expense (recovery)                              9</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Interest on long term debt</t>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="D524" t="inlineStr"/>
@@ -54343,19 +54311,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J524" s="5" t="n">
+        <v>-0.151</v>
       </c>
       <c r="K524" s="5" t="n">
-        <v>0.316</v>
+        <v>0.233</v>
       </c>
       <c r="L524" s="5" t="n">
-        <v>0.278</v>
+        <v>-0.173</v>
       </c>
       <c r="M524" s="5" t="n">
-        <v>0.324</v>
+        <v>0.333</v>
       </c>
       <c r="N524" t="inlineStr">
         <is>
@@ -54396,12 +54362,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Finance expenses include the following</t>
+          <t>Income tax expense (recovery)                              9</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Finance expenses $</t>
+          <t>Income tax expense (recovery)                              9 total</t>
         </is>
       </c>
       <c r="D525" t="inlineStr"/>
@@ -54431,16 +54397,16 @@
         </is>
       </c>
       <c r="J525" s="5" t="n">
-        <v>0.18</v>
+        <v>0.124</v>
       </c>
       <c r="K525" s="5" t="n">
-        <v>0.349</v>
+        <v>-0.039</v>
       </c>
       <c r="L525" s="5" t="n">
-        <v>0.333</v>
+        <v>-0.348</v>
       </c>
       <c r="M525" s="5" t="n">
-        <v>0.327</v>
+        <v>0.262</v>
       </c>
       <c r="N525" t="inlineStr">
         <is>
@@ -54481,47 +54447,59 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax expense (recovery)                              9</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Net income (loss) and comprehensive income (loss) $</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E526" s="5" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="F526" s="5" t="n">
-        <v>-0.452</v>
-      </c>
-      <c r="G526" s="5" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="H526" s="5" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="I526" s="5" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="J526" s="5" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="K526" s="5" t="n">
-        <v>0.123</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L526" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="M526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.02</v>
+      </c>
+      <c r="M526" s="5" t="n">
+        <v>0.36</v>
       </c>
       <c r="N526" t="inlineStr">
         <is>
@@ -54562,17 +54540,17 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)                              9</t>
+          <t>Per share amounts</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Basic and diluted 10 $</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -54600,19 +54578,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J527" s="5" t="n">
-        <v>-1.075</v>
-      </c>
-      <c r="K527" s="5" t="n">
-        <v>-0.453</v>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L527" s="5" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="M527" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.5e-07</v>
+      </c>
+      <c r="M527" s="5" t="n">
+        <v>5e-08</v>
       </c>
       <c r="N527" t="inlineStr">
         <is>
@@ -54653,19 +54633,15 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Finance expenses include the following</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Basic and diluted 10 $</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Interest on Operating Facility $</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
           <t>-</t>
@@ -54691,19 +54667,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J528" s="5" t="n">
-        <v>-1.6e-07</v>
-      </c>
-      <c r="K528" s="5" t="n">
-        <v>-7e-08</v>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L528" s="5" t="n">
-        <v>-1.5e-07</v>
-      </c>
-      <c r="M528" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.055</v>
+      </c>
+      <c r="M528" s="5" t="n">
+        <v>0.003</v>
       </c>
       <c r="N528" t="inlineStr">
         <is>
@@ -54749,7 +54727,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Interest on operating facility $</t>
+          <t>Interest on long term debt</t>
         </is>
       </c>
       <c r="D529" t="inlineStr"/>
@@ -54784,15 +54762,13 @@
         </is>
       </c>
       <c r="K529" s="5" t="n">
-        <v>0.033</v>
+        <v>0.316</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="M529" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.278</v>
+      </c>
+      <c r="M529" s="5" t="n">
+        <v>0.324</v>
       </c>
       <c r="N529" t="inlineStr">
         <is>
@@ -54831,17 +54807,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr"/>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Finance expenses include the following</t>
+        </is>
+      </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Net revenue 4 $</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Finance expenses $</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
           <t>-</t>
@@ -54868,20 +54844,16 @@
         </is>
       </c>
       <c r="J530" s="5" t="n">
-        <v>39.582</v>
+        <v>0.18</v>
       </c>
       <c r="K530" s="5" t="n">
-        <v>43.126</v>
-      </c>
-      <c r="L530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.349</v>
+      </c>
+      <c r="L530" s="5" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M530" s="5" t="n">
+        <v>0.327</v>
       </c>
       <c r="N530" t="inlineStr">
         <is>
@@ -54920,52 +54892,44 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B531" t="inlineStr"/>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Cost of sales 5, 25</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E531" s="5" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="F531" s="5" t="n">
+        <v>-0.452</v>
+      </c>
+      <c r="G531" s="5" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="H531" s="5" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="I531" s="5" t="n">
+        <v>0.351</v>
       </c>
       <c r="J531" s="5" t="n">
-        <v>21.819</v>
+        <v>0.241</v>
       </c>
       <c r="K531" s="5" t="n">
-        <v>24.477</v>
-      </c>
-      <c r="L531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.123</v>
+      </c>
+      <c r="L531" s="5" t="n">
+        <v>0.002</v>
       </c>
       <c r="M531" t="inlineStr">
         <is>
@@ -55009,15 +54973,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr"/>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)                              9</t>
+        </is>
+      </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Net loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -55025,28 +54993,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F532" s="5" t="n">
-        <v>23.798</v>
-      </c>
-      <c r="G532" s="5" t="n">
-        <v>24.908</v>
-      </c>
-      <c r="H532" s="5" t="n">
-        <v>21.327</v>
-      </c>
-      <c r="I532" s="5" t="n">
-        <v>17.825</v>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J532" s="5" t="n">
-        <v>17.763</v>
+        <v>-1.075</v>
       </c>
       <c r="K532" s="5" t="n">
-        <v>18.649</v>
-      </c>
-      <c r="L532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.453</v>
+      </c>
+      <c r="L532" s="5" t="n">
+        <v>-1.02</v>
       </c>
       <c r="M532" t="inlineStr">
         <is>
@@ -55092,17 +55066,17 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>General and administrative 7, 25</t>
+          <t>Basic and diluted 10 $</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -55131,15 +55105,13 @@
         </is>
       </c>
       <c r="J533" s="5" t="n">
-        <v>5.212</v>
+        <v>-1.6e-07</v>
       </c>
       <c r="K533" s="5" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="L533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7e-08</v>
+      </c>
+      <c r="L533" s="5" t="n">
+        <v>-1.5e-07</v>
       </c>
       <c r="M533" t="inlineStr">
         <is>
@@ -55190,7 +55162,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Interest on long-term debt $</t>
+          <t>Interest on operating facility $</t>
         </is>
       </c>
       <c r="D534" t="inlineStr"/>
@@ -55219,16 +55191,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J534" s="5" t="n">
-        <v>0.112</v>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K534" s="5" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="L534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033</v>
+      </c>
+      <c r="L534" s="5" t="n">
+        <v>0.055</v>
       </c>
       <c r="M534" t="inlineStr">
         <is>
@@ -55272,17 +55244,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>Finance expenses include the following</t>
-        </is>
-      </c>
+      <c r="B535" t="inlineStr"/>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Interest on operating facility</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr"/>
+          <t>Net revenue 4 $</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -55309,10 +55281,10 @@
         </is>
       </c>
       <c r="J535" s="5" t="n">
-        <v>0.068</v>
+        <v>39.582</v>
       </c>
       <c r="K535" s="5" t="n">
-        <v>0.033</v>
+        <v>43.126</v>
       </c>
       <c r="L535" t="inlineStr">
         <is>
@@ -55364,12 +55336,12 @@
       <c r="B536" t="inlineStr"/>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Net revenue (Notes 3.2 and 4) $</t>
+          <t>Cost of sales 5, 25</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -55382,22 +55354,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G536" s="5" t="n">
-        <v>46.057</v>
-      </c>
-      <c r="H536" s="5" t="n">
-        <v>41.587</v>
-      </c>
-      <c r="I536" s="5" t="n">
-        <v>36.755</v>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J536" s="5" t="n">
-        <v>39.594</v>
-      </c>
-      <c r="K536" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.819</v>
+      </c>
+      <c r="K536" s="5" t="n">
+        <v>24.477</v>
       </c>
       <c r="L536" t="inlineStr">
         <is>
@@ -55449,12 +55425,12 @@
       <c r="B537" t="inlineStr"/>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Cost of sales (Notes 5 and 23)</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -55462,29 +55438,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F537" s="5" t="n">
+        <v>23.798</v>
+      </c>
+      <c r="G537" s="5" t="n">
+        <v>24.908</v>
       </c>
       <c r="H537" s="5" t="n">
-        <v>20.26</v>
+        <v>21.327</v>
       </c>
       <c r="I537" s="5" t="n">
-        <v>18.93</v>
+        <v>17.825</v>
       </c>
       <c r="J537" s="5" t="n">
-        <v>21.965</v>
-      </c>
-      <c r="K537" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.763</v>
+      </c>
+      <c r="K537" s="5" t="n">
+        <v>18.649</v>
       </c>
       <c r="L537" t="inlineStr">
         <is>
@@ -55540,12 +55510,12 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Selling expenses (Note 6)</t>
+          <t>General and administrative 7, 25</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>SellingExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -55563,19 +55533,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H538" s="5" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="I538" s="5" t="n">
-        <v>12.335</v>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J538" s="5" t="n">
-        <v>13.187</v>
-      </c>
-      <c r="K538" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.212</v>
+      </c>
+      <c r="K538" s="5" t="n">
+        <v>5.72</v>
       </c>
       <c r="L538" t="inlineStr">
         <is>
@@ -55626,19 +55598,15 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Finance expenses include the following</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>General and administrative (Notes 7 and 23)</t>
-        </is>
-      </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Interest on long-term debt $</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -55654,19 +55622,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H539" s="5" t="n">
-        <v>4.821</v>
-      </c>
-      <c r="I539" s="5" t="n">
-        <v>4.489</v>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J539" s="5" t="n">
-        <v>5.212</v>
-      </c>
-      <c r="K539" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.112</v>
+      </c>
+      <c r="K539" s="5" t="n">
+        <v>0.316</v>
       </c>
       <c r="L539" t="inlineStr">
         <is>
@@ -55717,19 +55687,15 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Finance expenses include the following</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Operating profit (loss)</t>
-        </is>
-      </c>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Interest on operating facility</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -55750,16 +55716,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I540" s="5" t="n">
-        <v>0.715</v>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J540" s="5" t="n">
-        <v>-1.146</v>
-      </c>
-      <c r="K540" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.068</v>
+      </c>
+      <c r="K540" s="5" t="n">
+        <v>0.033</v>
       </c>
       <c r="L540" t="inlineStr">
         <is>
@@ -55808,17 +55774,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Finance expenses (income) (Note 8)</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr"/>
+          <t>Net revenue (Notes 3.2 and 4) $</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -55829,19 +55795,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G541" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G541" s="5" t="n">
+        <v>46.057</v>
       </c>
       <c r="H541" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>41.587</v>
       </c>
       <c r="I541" s="5" t="n">
-        <v>-0.036</v>
+        <v>36.755</v>
       </c>
       <c r="J541" s="5" t="n">
-        <v>0.18</v>
+        <v>39.594</v>
       </c>
       <c r="K541" t="inlineStr">
         <is>
@@ -55895,38 +55859,40 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B542" t="inlineStr"/>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Cost of sales (Notes 5 and 23)</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E542" s="5" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="F542" s="5" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="G542" s="5" t="n">
-        <v>0.147</v>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H542" s="5" t="n">
-        <v>0.109</v>
+        <v>20.26</v>
       </c>
       <c r="I542" s="5" t="n">
-        <v>0.153</v>
+        <v>18.93</v>
       </c>
       <c r="J542" s="5" t="n">
-        <v>0.129</v>
+        <v>21.965</v>
       </c>
       <c r="K542" t="inlineStr">
         <is>
@@ -55987,12 +55953,12 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Current income tax expense (Note 9)</t>
+          <t>Selling expenses (Note 6)</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>SellingExpense</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -56005,17 +55971,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G543" s="5" t="n">
-        <v>0.426</v>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H543" s="5" t="n">
-        <v>2.485</v>
+        <v>12.91</v>
       </c>
       <c r="I543" s="5" t="n">
-        <v>0.279</v>
+        <v>12.335</v>
       </c>
       <c r="J543" s="5" t="n">
-        <v>0.275</v>
+        <v>13.187</v>
       </c>
       <c r="K543" t="inlineStr">
         <is>
@@ -56076,12 +56044,12 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery) (Note 9)</t>
+          <t>General and administrative (Notes 7 and 23)</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -56094,17 +56062,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G544" s="5" t="n">
-        <v>1.168</v>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H544" s="5" t="n">
-        <v>-1.586</v>
+        <v>4.821</v>
       </c>
       <c r="I544" s="5" t="n">
-        <v>0.046</v>
+        <v>4.489</v>
       </c>
       <c r="J544" s="5" t="n">
-        <v>-0.151</v>
+        <v>5.212</v>
       </c>
       <c r="K544" t="inlineStr">
         <is>
@@ -56160,24 +56130,28 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Net income (loss) per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
+          <t>Operating profit (loss)</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E545" s="5" t="n">
-        <v>-1.36e-06</v>
-      </c>
-      <c r="F545" s="5" t="n">
-        <v>4.2e-07</v>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
@@ -56190,10 +56164,10 @@
         </is>
       </c>
       <c r="I545" s="5" t="n">
-        <v>9e-08</v>
+        <v>0.715</v>
       </c>
       <c r="J545" s="5" t="n">
-        <v>-1.6e-07</v>
+        <v>-1.146</v>
       </c>
       <c r="K545" t="inlineStr">
         <is>
@@ -56254,33 +56228,33 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Operating profit</t>
-        </is>
-      </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E546" s="5" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="F546" s="5" t="n">
-        <v>3.343</v>
-      </c>
-      <c r="G546" s="5" t="n">
-        <v>5.618</v>
+          <t>Finance expenses (income) (Note 8)</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H546" s="5" t="n">
-        <v>3.282</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I546" s="5" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="J546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.036</v>
+      </c>
+      <c r="J546" s="5" t="n">
+        <v>0.18</v>
       </c>
       <c r="K546" t="inlineStr">
         <is>
@@ -56341,35 +56315,31 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E547" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E547" s="5" t="n">
+        <v>0.108</v>
       </c>
       <c r="F547" s="5" t="n">
-        <v>3.49</v>
+        <v>0.164</v>
       </c>
       <c r="G547" s="5" t="n">
-        <v>5.729</v>
+        <v>0.147</v>
       </c>
       <c r="H547" s="5" t="n">
-        <v>3.45</v>
+        <v>0.109</v>
       </c>
       <c r="I547" s="5" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="J547" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.153</v>
+      </c>
+      <c r="J547" s="5" t="n">
+        <v>0.129</v>
       </c>
       <c r="K547" t="inlineStr">
         <is>
@@ -56430,31 +56400,35 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income for the period $</t>
-        </is>
-      </c>
-      <c r="D548" t="inlineStr"/>
+          <t>Current income tax expense (Note 9)</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F548" s="5" t="n">
-        <v>2.533</v>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G548" s="5" t="n">
-        <v>4.135</v>
+        <v>0.426</v>
       </c>
       <c r="H548" s="5" t="n">
-        <v>2.551</v>
+        <v>2.485</v>
       </c>
       <c r="I548" s="5" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="J548" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.279</v>
+      </c>
+      <c r="J548" s="5" t="n">
+        <v>0.275</v>
       </c>
       <c r="K548" t="inlineStr">
         <is>
@@ -56510,17 +56484,17 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
+          <t>Deferred income tax expense (recovery) (Note 9)</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -56528,22 +56502,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F549" s="5" t="n">
-        <v>4.2e-07</v>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G549" s="5" t="n">
-        <v>6.800000000000001e-07</v>
+        <v>1.168</v>
       </c>
       <c r="H549" s="5" t="n">
-        <v>4.2e-07</v>
+        <v>-1.586</v>
       </c>
       <c r="I549" s="5" t="n">
-        <v>9e-08</v>
-      </c>
-      <c r="J549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.046</v>
+      </c>
+      <c r="J549" s="5" t="n">
+        <v>-0.151</v>
       </c>
       <c r="K549" t="inlineStr">
         <is>
@@ -56597,42 +56571,42 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B550" t="inlineStr"/>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Net income (loss) per share</t>
+        </is>
+      </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Cost of sales (Notes 5 and 24)</t>
+          <t>Basic and diluted $</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G550" s="5" t="n">
-        <v>21.149</v>
-      </c>
-      <c r="H550" s="5" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E550" s="5" t="n">
+        <v>-1.36e-06</v>
+      </c>
+      <c r="F550" s="5" t="n">
+        <v>4.2e-07</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I550" s="5" t="n">
+        <v>9e-08</v>
+      </c>
+      <c r="J550" s="5" t="n">
+        <v>-1.6e-07</v>
       </c>
       <c r="K550" t="inlineStr">
         <is>
@@ -56693,30 +56667,28 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Selling expenses (Notes 6 and 23)</t>
+          <t>Operating profit</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>SellingExpense</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E551" s="5" t="n">
-        <v>15.215</v>
+        <v>4.133</v>
       </c>
       <c r="F551" s="5" t="n">
-        <v>15.835</v>
+        <v>3.343</v>
       </c>
       <c r="G551" s="5" t="n">
-        <v>13.987</v>
+        <v>5.618</v>
       </c>
       <c r="H551" s="5" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="I551" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.282</v>
+      </c>
+      <c r="I551" s="5" t="n">
+        <v>0.715</v>
       </c>
       <c r="J551" t="inlineStr">
         <is>
@@ -56782,30 +56754,30 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>General and administrative (Notes 7 and 24)</t>
+          <t>Income before income taxes</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E552" s="5" t="n">
-        <v>4.775</v>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F552" s="5" t="n">
-        <v>4.281</v>
+        <v>3.49</v>
       </c>
       <c r="G552" s="5" t="n">
-        <v>4.945</v>
+        <v>5.729</v>
       </c>
       <c r="H552" s="5" t="n">
-        <v>4.821</v>
-      </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.45</v>
+      </c>
+      <c r="I552" s="5" t="n">
+        <v>0.949</v>
       </c>
       <c r="J552" t="inlineStr">
         <is>
@@ -56871,26 +56843,26 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Finance costs (Note 8)</t>
+          <t>Net income and comprehensive income for the period $</t>
         </is>
       </c>
       <c r="D553" t="inlineStr"/>
-      <c r="E553" s="5" t="n">
-        <v>2.558</v>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F553" s="5" t="n">
-        <v>0.141</v>
+        <v>2.533</v>
       </c>
       <c r="G553" s="5" t="n">
-        <v>0.093</v>
+        <v>4.135</v>
       </c>
       <c r="H553" s="5" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.551</v>
+      </c>
+      <c r="I553" s="5" t="n">
+        <v>0.624</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -56951,33 +56923,35 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Dec. 30          Dec. 30</t>
+          <t>Net income per share</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Interest on long-term debt $</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F554" s="5" t="n">
-        <v>0.13</v>
+        <v>4.2e-07</v>
       </c>
       <c r="G554" s="5" t="n">
-        <v>0.101</v>
+        <v>6.800000000000001e-07</v>
       </c>
       <c r="H554" s="5" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="I554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.2e-07</v>
+      </c>
+      <c r="I554" s="5" t="n">
+        <v>9e-08</v>
       </c>
       <c r="J554" t="inlineStr">
         <is>
@@ -57036,30 +57010,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>Dec. 30          Dec. 30</t>
-        </is>
-      </c>
+      <c r="B555" t="inlineStr"/>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Interest on operating facility</t>
-        </is>
-      </c>
-      <c r="D555" t="inlineStr"/>
+          <t>Cost of sales (Notes 5 and 24)</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E555" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F555" s="5" t="n">
-        <v>0.011</v>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G555" s="5" t="n">
-        <v>-0.008</v>
+        <v>21.149</v>
       </c>
       <c r="H555" s="5" t="n">
-        <v>-0.025</v>
+        <v>20.26</v>
       </c>
       <c r="I555" t="inlineStr">
         <is>
@@ -57125,28 +57101,30 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Dec. 30          Dec. 30</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Finance costs $</t>
-        </is>
-      </c>
-      <c r="D556" t="inlineStr"/>
-      <c r="E556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Selling expenses (Notes 6 and 23)</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>SellingExpense</t>
+        </is>
+      </c>
+      <c r="E556" s="5" t="n">
+        <v>15.215</v>
       </c>
       <c r="F556" s="5" t="n">
-        <v>0.141</v>
+        <v>15.835</v>
       </c>
       <c r="G556" s="5" t="n">
-        <v>0.093</v>
+        <v>13.987</v>
       </c>
       <c r="H556" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>12.91</v>
       </c>
       <c r="I556" t="inlineStr">
         <is>
@@ -57210,32 +57188,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B557" t="inlineStr"/>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Net revenue (Note 3.2) $</t>
+          <t>General and administrative (Notes 7 and 24)</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E557" s="5" t="n">
+        <v>4.775</v>
       </c>
       <c r="F557" s="5" t="n">
-        <v>45.183</v>
+        <v>4.281</v>
       </c>
       <c r="G557" s="5" t="n">
-        <v>46.057</v>
-      </c>
-      <c r="H557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.945</v>
+      </c>
+      <c r="H557" s="5" t="n">
+        <v>4.821</v>
       </c>
       <c r="I557" t="inlineStr">
         <is>
@@ -57299,32 +57277,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr"/>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Cost of sales (Note 4)</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Finance costs (Note 8)</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
+      <c r="E558" s="5" t="n">
+        <v>2.558</v>
       </c>
       <c r="F558" s="5" t="n">
-        <v>21.385</v>
+        <v>0.141</v>
       </c>
       <c r="G558" s="5" t="n">
-        <v>21.149</v>
-      </c>
-      <c r="H558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.093</v>
+      </c>
+      <c r="H558" s="5" t="n">
+        <v>0.008999999999999999</v>
       </c>
       <c r="I558" t="inlineStr">
         <is>
@@ -57390,34 +57364,28 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Dec. 30          Dec. 30</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Selling expenses (Notes 5 and 22)</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>SellingExpense</t>
-        </is>
-      </c>
+          <t>Interest on long-term debt $</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F559" s="5" t="n">
-        <v>15.835</v>
+        <v>0.13</v>
       </c>
       <c r="G559" s="5" t="n">
-        <v>13.987</v>
-      </c>
-      <c r="H559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.101</v>
+      </c>
+      <c r="H559" s="5" t="n">
+        <v>0.034</v>
       </c>
       <c r="I559" t="inlineStr">
         <is>
@@ -57483,34 +57451,28 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Dec. 30          Dec. 30</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>General and administrative (Notes 6 and 23)</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Interest on operating facility</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F560" s="5" t="n">
-        <v>4.281</v>
+        <v>0.011</v>
       </c>
       <c r="G560" s="5" t="n">
-        <v>4.945</v>
-      </c>
-      <c r="H560" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008</v>
+      </c>
+      <c r="H560" s="5" t="n">
+        <v>-0.025</v>
       </c>
       <c r="I560" t="inlineStr">
         <is>
@@ -57576,12 +57538,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Dec. 30          Dec. 30</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Finance costs (Note 7)</t>
+          <t>Finance costs $</t>
         </is>
       </c>
       <c r="D561" t="inlineStr"/>
@@ -57596,10 +57558,8 @@
       <c r="G561" s="5" t="n">
         <v>0.093</v>
       </c>
-      <c r="H561" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H561" s="5" t="n">
+        <v>0.008999999999999999</v>
       </c>
       <c r="I561" t="inlineStr">
         <is>
@@ -57663,19 +57623,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B562" t="inlineStr"/>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Income tax expense (Note 8)</t>
+          <t>Net revenue (Note 3.2) $</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -57684,10 +57640,10 @@
         </is>
       </c>
       <c r="F562" s="5" t="n">
-        <v>0.957</v>
+        <v>45.183</v>
       </c>
       <c r="G562" s="5" t="n">
-        <v>1.594</v>
+        <v>46.057</v>
       </c>
       <c r="H562" t="inlineStr">
         <is>
@@ -57756,31 +57712,27 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>Big Rock Brewery Inc.</t>
-        </is>
-      </c>
+      <c r="B563" t="inlineStr"/>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Net revenue (Note 4.2) $</t>
+          <t>Cost of sales (Note 4)</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E563" s="5" t="n">
-        <v>45.13</v>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F563" s="5" t="n">
-        <v>45.183</v>
-      </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.385</v>
+      </c>
+      <c r="G563" s="5" t="n">
+        <v>21.149</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
@@ -57851,29 +57803,29 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Big Rock Brewery Inc.</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Cost of sales (Note 5)</t>
+          <t>Selling expenses (Notes 5 and 22)</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E564" s="5" t="n">
-        <v>207352.011</v>
+          <t>SellingExpense</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F564" s="5" t="n">
-        <v>21.385</v>
-      </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.835</v>
+      </c>
+      <c r="G564" s="5" t="n">
+        <v>13.987</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
@@ -57944,29 +57896,29 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Big Rock Brewery Inc.</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>General and administrative (Notes 6 and 23)</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E565" s="5" t="n">
-        <v>24.395</v>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F565" s="5" t="n">
-        <v>23.798</v>
-      </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.281</v>
+      </c>
+      <c r="G565" s="5" t="n">
+        <v>4.945</v>
       </c>
       <c r="H565" t="inlineStr">
         <is>
@@ -58042,22 +57994,20 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Fair value loss on trust units liability (Notes 16 and 22)</t>
+          <t>Finance costs (Note 7)</t>
         </is>
       </c>
       <c r="D566" t="inlineStr"/>
-      <c r="E566" s="5" t="n">
-        <v>10.686</v>
-      </c>
-      <c r="F566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F566" s="5" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="G566" s="5" t="n">
+        <v>0.093</v>
       </c>
       <c r="H566" t="inlineStr">
         <is>
@@ -58133,22 +58083,24 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Fair value loss on share based payments liability (Notes 16 and 22)</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr"/>
-      <c r="E567" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Income tax expense (Note 8)</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F567" s="5" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G567" s="5" t="n">
+        <v>1.594</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
@@ -58219,24 +58171,24 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Big Rock Brewery Inc.</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery) (Note 9)</t>
+          <t>Net revenue (Note 4.2) $</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E568" s="5" t="n">
-        <v>-0.658</v>
+        <v>45.13</v>
       </c>
       <c r="F568" s="5" t="n">
-        <v>0.957</v>
+        <v>45.183</v>
       </c>
       <c r="G568" t="inlineStr">
         <is>
@@ -58312,24 +58264,24 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Big Rock Brewery Inc.</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) for the period $</t>
+          <t>Cost of sales (Note 5)</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E569" s="5" t="n">
-        <v>-8.198</v>
+        <v>207352.011</v>
       </c>
       <c r="F569" s="5" t="n">
-        <v>2.533</v>
+        <v>21.385</v>
       </c>
       <c r="G569" t="inlineStr">
         <is>
@@ -58405,20 +58357,24 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Dec. 30          Dec. 31</t>
+          <t>Big Rock Brewery Inc.</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Interest on long-term debt $</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E570" s="5" t="n">
-        <v>0.142</v>
+        <v>24.395</v>
       </c>
       <c r="F570" s="5" t="n">
-        <v>0.13</v>
+        <v>23.798</v>
       </c>
       <c r="G570" t="inlineStr">
         <is>
@@ -58494,20 +58450,22 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Dec. 30          Dec. 31</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Interest on operating facility</t>
+          <t>Fair value loss on trust units liability (Notes 16 and 22)</t>
         </is>
       </c>
       <c r="D571" t="inlineStr"/>
       <c r="E571" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F571" s="5" t="n">
-        <v>0.011</v>
+        <v>10.686</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
@@ -58583,17 +58541,17 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Dec. 30          Dec. 31</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Distributions to shareholders</t>
+          <t>Fair value loss on share based payments liability (Notes 16 and 22)</t>
         </is>
       </c>
       <c r="D572" t="inlineStr"/>
       <c r="E572" s="5" t="n">
-        <v>2.414</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -58674,82 +58632,537 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery) (Note 9)</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E573" s="5" t="n">
+        <v>-0.658</v>
+      </c>
+      <c r="F573" s="5" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Net income (loss) and comprehensive income (loss) for the period $</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E574" s="5" t="n">
+        <v>-8.198</v>
+      </c>
+      <c r="F574" s="5" t="n">
+        <v>2.533</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
           <t>Dec. 30          Dec. 31</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Interest on long-term debt $</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr"/>
+      <c r="E575" s="5" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="F575" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Dec. 30          Dec. 31</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Interest on operating facility</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F576" s="5" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Dec. 30          Dec. 31</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Distributions to shareholders</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr"/>
+      <c r="E577" s="5" t="n">
+        <v>2.414</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Dec. 30          Dec. 31</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
         <is>
           <t>Finance costs $</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
-      <c r="E573" s="5" t="n">
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" s="5" t="n">
         <v>2.558</v>
       </c>
-      <c r="F573" s="5" t="n">
+      <c r="F578" s="5" t="n">
         <v>0.141</v>
       </c>
-      <c r="G573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S573" t="inlineStr">
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
         <is>
           <t>-</t>
         </is>
